--- a/02_DIA_inicio_2026_analisis_assets/rbd_9734_escuela-raul-saez-saez_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9734_escuela-raul-saez-saez_nt1_rubricas.xlsx
@@ -1884,13 +1884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31558032-BDEF-412B-8973-0407304DC04E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{895D7F6B-415B-4EA7-8962-5A03B45E2136}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A93D89-42FE-4D5E-B8D1-502B3F9B59DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00A377FF-9CA7-4181-A81F-C055237EEA57}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FFF1A75-5B40-4086-A98A-C09ECB0994C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71948A60-288D-4CEC-8939-D8846A859AE1}"/>
 </file>